--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>606_康乃馨橙光_orange_undefined_20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03106553101070</v>
+        <v>03106553101073</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,86 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>890_康乃馨红绸_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F18" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F19" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F20" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +658,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03106553101073</v>
+        <v>0310655310107333610533330</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -600,6 +600,9 @@
       <c r="C21" t="str">
         <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -658,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0310655310107333610533330</v>
+        <v>0310655310107333610533332</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -601,7 +601,7 @@
         <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F21" t="str">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0310655310107333610533332</v>
+        <v>03106553101073336105333321</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -604,9 +604,91 @@
         <v>21</v>
       </c>
     </row>
+    <row r="22" xml:space="preserve">
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="C23" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>71_霜雪mini_Snowy_Gerbera L._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>4</v>
+      </c>
+      <c r="C29" t="str">
+        <v>326_红继木_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>882_乒乓菊黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -661,7 +743,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03106553101073336105333321</v>
+        <v>031065531010733361053333215533333530</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -685,6 +685,9 @@
       <c r="C31" t="str">
         <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -743,7 +746,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>031065531010733361053333215533333530</v>
+        <v>031065531010733361053333215533333533</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -689,9 +689,90 @@
         <v>3</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>590_洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>387_洋甘菊_Chamomile_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>84_堪培拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>5</v>
+      </c>
+      <c r="C40" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="C41" t="str" xml:space="preserve">
+        <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
+（dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -746,7 +827,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>031065531010733361053333215533333533</v>
+        <v>03106553101073336105333321553333353355313553350</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -769,6 +769,9 @@
         <v xml:space="preserve">349_千层金绿_Melaleuca bracteata
 （dyed orange）_Melaleuca bracteata F.Muell._1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -827,7 +830,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03106553101073336105333321553333353355313553350</v>
+        <v>03106553101073336105333321553333353355313553355</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -773,9 +773,73 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>383_油画向日葵_sunflower black_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>325_小盼草_Northern Sea Oats_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L49"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -830,7 +894,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>03106553101073336105333321553333353355313553355</v>
+        <v>03106553101073336105333321553333353355313553355553635510</v>
       </c>
     </row>
   </sheetData>
